--- a/source/remark_nik.xlsx
+++ b/source/remark_nik.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395"/>
+    <workbookView windowWidth="19635" windowHeight="8115"/>
   </bookViews>
   <sheets>
     <sheet name="Remark NIK" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="621">
   <si>
     <t>link</t>
   </si>
@@ -41,34 +41,1855 @@
     <t>timpa_remark</t>
   </si>
   <si>
-    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/0010eb4e-9ec0-47ef-8236-70df81da8a32/edit</t>
-  </si>
-  <si>
-    <t>NANDA JAGO SAPUTRA</t>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4f850fae-3790-43a5-b920-db3fe52f935b/edit</t>
+  </si>
+  <si>
+    <t>HASAN</t>
   </si>
   <si>
     <t>#0</t>
   </si>
   <si>
-    <t>AKBAR NUR ABDILLAH</t>
-  </si>
-  <si>
-    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/00df9633-922e-4860-b90c-1bddb4df4438/edit</t>
-  </si>
-  <si>
-    <t>BERNADETA SOGIN</t>
-  </si>
-  <si>
-    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/010dedc1-d3c3-4578-82e8-4d0ef8ddb35a/edit</t>
-  </si>
-  <si>
-    <t>SEMADEN</t>
-  </si>
-  <si>
-    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/011d4de2-4ca3-4b38-9520-56de7d9c2241/edit</t>
-  </si>
-  <si>
-    <t>SABINA AJIN</t>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8d515ca5-c9a5-43bb-8c0b-070715cd8ef0/edit</t>
+  </si>
+  <si>
+    <t>Dela aryani</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c6bb9f99-fd2a-4b6f-9e4f-d7a877c3e7d5/edit</t>
+  </si>
+  <si>
+    <t>MAHMUDIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9ae9a354-5b54-4d35-bd89-57f69c3ab5cf/edit</t>
+  </si>
+  <si>
+    <t>DWI ARIF SULISTIONO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4e6e7716-48e2-4b40-9032-de42134260dc/edit</t>
+  </si>
+  <si>
+    <t>THOMAS DIMA BERO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9ee4ae45-237c-47bc-b097-fbf1318041fb/edit</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ARIQIN ALKARIM</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/810193fa-ecc6-4786-94d0-c72d146cb593/edit</t>
+  </si>
+  <si>
+    <t>HARI PURNOMO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/e771d4e4-5044-4f15-815f-0c85aadb9a1d/edit</t>
+  </si>
+  <si>
+    <t>JEJEN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/92df8628-9ece-43e5-9f08-b28ac5883b26/edit</t>
+  </si>
+  <si>
+    <t>AJAM</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4521cf99-3867-4839-8847-7f6d1f6f6f14/edit</t>
+  </si>
+  <si>
+    <t>HERKULANUS PILO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/1d75d124-4cd2-4218-b37f-584711ef61e9/edit</t>
+  </si>
+  <si>
+    <t>Gabriel immanuel</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/97a11751-a300-41e0-aaed-576cba37caa3/edit</t>
+  </si>
+  <si>
+    <t>Muhammad afran sutrisno</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4f901cac-a5ae-4326-8e94-d7fa40bd9917/edit</t>
+  </si>
+  <si>
+    <t>Mariana isa</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b20ae81c-a5af-4bb7-910c-be66b792ea9b/edit</t>
+  </si>
+  <si>
+    <t>SAHRUL GUNAWAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c544c347-c1be-4eac-956b-269b71c7d284/edit</t>
+  </si>
+  <si>
+    <t>FITRA NOKA BUDSIHERDA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/d6abae08-6299-48ca-8f0e-e79e929d04cc/edit</t>
+  </si>
+  <si>
+    <t>ANTONI ABI</t>
+  </si>
+  <si>
+    <t>YERIKHO ELIEZER BERO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4711fd2f-dbef-4bec-8ffc-006126e4cb89/edit</t>
+  </si>
+  <si>
+    <t>JUNAIDI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/628897d2-853e-4850-abc0-bc7c385322d9/edit</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ZAIDAN ILLIANSYAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8dfad4ca-50f2-4da6-8cfa-63397b9c5e34/edit</t>
+  </si>
+  <si>
+    <t>KEANU AUFA RIZQI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a5c2e4b0-912e-4100-82e6-bfba887bc7b3/edit</t>
+  </si>
+  <si>
+    <t>RENDI SETIAWAN</t>
+  </si>
+  <si>
+    <t>IYON</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/ddd3321a-9d08-4bc1-97f3-a7c2e210cdad/edit</t>
+  </si>
+  <si>
+    <t>DIONISIUS SETIAWAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9a2e481c-86a6-44e3-a99f-2678850ca31b/edit</t>
+  </si>
+  <si>
+    <t>ANEN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/49133a6f-addf-4f8d-9cbc-dc6258aec66e/edit</t>
+  </si>
+  <si>
+    <t>SUHARMANTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7b0376a7-145c-4304-9899-1d1ef0c5e405/edit</t>
+  </si>
+  <si>
+    <t>MAYOR</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8bccc67a-edc0-4311-9b47-9f56523d7950/edit</t>
+  </si>
+  <si>
+    <t>FADILLA MAULINDRA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5019b26c-7d77-4d1a-8813-9f6e8e7a9aeb/edit</t>
+  </si>
+  <si>
+    <t>AKATO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b90b5992-f3ef-4f9b-af08-f43a6f23f75c/edit</t>
+  </si>
+  <si>
+    <t>ADIL SYAHYUGA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/90ea6433-0b00-42d9-a140-f854575e718c/edit</t>
+  </si>
+  <si>
+    <t>TITUS SIYO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/774e4978-479d-4826-916f-7ca88d56d8d2/edit</t>
+  </si>
+  <si>
+    <t>AGUS MIRANDA</t>
+  </si>
+  <si>
+    <t>MUHAMMAD SYAKIR</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7a3bbaf2-3e76-4fbb-93b5-9e56eef96402/edit</t>
+  </si>
+  <si>
+    <t>PIPIT</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/f1b2b2de-ff02-430f-bb9f-b56d1b1b8c4c/edit</t>
+  </si>
+  <si>
+    <t>DHAFA ALDINA RIZKY</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a35f7295-82a4-41ec-9d1b-c2328f9454b7/edit</t>
+  </si>
+  <si>
+    <t>ZIYAD AUFA MUTTAQY</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/06f6990c-e5e4-4cf0-a9a2-3a6e54751105/edit</t>
+  </si>
+  <si>
+    <t>PAHRULLAH NURCAHYA AHMADINATA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/464b397e-e861-460e-8618-ecf379082855/edit</t>
+  </si>
+  <si>
+    <t>MADI SUGANDA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/41c60e4d-1a13-4266-a704-87cc27e10b26/edit</t>
+  </si>
+  <si>
+    <t>RAMBO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/371b1b4f-ac5d-41ca-8720-d42502ab19ae/edit</t>
+  </si>
+  <si>
+    <t>SUKONO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4115128e-cf7b-4d24-a7b2-d4785750adeb/edit</t>
+  </si>
+  <si>
+    <t>ANDRI STEPEN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b85453f0-d177-40a3-9238-394072f5adf7/edit</t>
+  </si>
+  <si>
+    <t>Sulthan al hanan</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b2f038ad-95a1-4264-a19b-d1a0313f4114/edit</t>
+  </si>
+  <si>
+    <t>DODI KURNIAWAN</t>
+  </si>
+  <si>
+    <t>ANDRICA FAJARRULLAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4d2c0a81-4c41-4573-9ec5-16372e78dc8d/edit</t>
+  </si>
+  <si>
+    <t>ARINI WIDYANINGRUM</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b66a003c-9215-43ef-9c9b-38e628c6c5b5/edit</t>
+  </si>
+  <si>
+    <t>Delvanius chandra</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/634bba25-8c5f-4619-b20d-ca5e6c95c65f/edit</t>
+  </si>
+  <si>
+    <t>GALUH AFRIASTINI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/ed71813a-fdca-4123-bce0-e375c44c7e68/edit</t>
+  </si>
+  <si>
+    <t>Yohana Asiang</t>
+  </si>
+  <si>
+    <t>LO WILI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/753e09d1-29a4-4e44-9842-b178bb247004/edit</t>
+  </si>
+  <si>
+    <t>KRISANTUS ANWAR</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a44a8d87-4ff2-4ccd-9e30-1112aa860972/edit</t>
+  </si>
+  <si>
+    <t>jeslyn anggelista putri</t>
+  </si>
+  <si>
+    <t>ERIKA APRILIA WILNA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a1de5efb-a946-4f3c-a9d5-fa2b8d379b14/edit</t>
+  </si>
+  <si>
+    <t>Yohana sain</t>
+  </si>
+  <si>
+    <t>Peronika olin</t>
+  </si>
+  <si>
+    <t>HERLINAWATI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a8b22747-c234-4c2f-b45a-f1a0fae951fd/edit</t>
+  </si>
+  <si>
+    <t>Lutvia azaria azhar</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/2ac50298-5fb3-403c-b3e8-2479f40e4269/edit</t>
+  </si>
+  <si>
+    <t>MAS JAMIAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/86d8bfe1-011a-4206-8e2a-c6f00fa838f4/edit</t>
+  </si>
+  <si>
+    <t>Kristina rosi</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9084c3df-2728-4c59-8418-7e1496362b96/edit</t>
+  </si>
+  <si>
+    <t>JUNIATI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4c3b57e8-2e94-4482-a029-06d9a35657f9/edit</t>
+  </si>
+  <si>
+    <t>Sriwati</t>
+  </si>
+  <si>
+    <t>ABIGAEL MARSYA SABDA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/0235eac1-803e-4731-869a-0cf0b6a4b685/edit</t>
+  </si>
+  <si>
+    <t>RONI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5cc4f4c2-786a-472f-b1f9-579bd78f09c5/edit</t>
+  </si>
+  <si>
+    <t>JENI FATMAWATI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b893dea4-cc17-4b39-88e3-2544a4311c9d/edit</t>
+  </si>
+  <si>
+    <t>DWI HANY DZAKIYYAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/be69010d-95b4-4223-9503-0070aabdfd58/edit</t>
+  </si>
+  <si>
+    <t>JELINA</t>
+  </si>
+  <si>
+    <t>DIVA AVILA OKTARIA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/12cc0642-1168-4a2f-8717-732388cd900a/edit</t>
+  </si>
+  <si>
+    <t>SUMARDI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/471c589e-6204-483d-ba9a-8a1dc5627484/edit</t>
+  </si>
+  <si>
+    <t>PRAMULIA RIZKING</t>
+  </si>
+  <si>
+    <t>KRISTINA WATI</t>
+  </si>
+  <si>
+    <t>CHOERUNNISSA</t>
+  </si>
+  <si>
+    <t>FATHIN AYUDIA QANITA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/d54e0766-e854-4967-8436-24d48f04c309/edit</t>
+  </si>
+  <si>
+    <t>SAKINAH</t>
+  </si>
+  <si>
+    <t>MIRNALISA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7011cd8f-8277-40d1-89cf-d2e05daa83b4/edit</t>
+  </si>
+  <si>
+    <t>VIA LESTARI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4d08086d-2045-439c-90ad-f4047eabe8e1/edit</t>
+  </si>
+  <si>
+    <t>ISTANTI</t>
+  </si>
+  <si>
+    <t>LO WINA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/3a581d38-b9e5-4b70-a791-deb4c7b1087c/edit</t>
+  </si>
+  <si>
+    <t>DWI APRILIANI KURNIA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/700a2026-fdde-4795-b9b9-6ae857b4f6cb/edit</t>
+  </si>
+  <si>
+    <t>I`IN SURYADI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a678c556-26ca-4374-868d-c256d7a405c5/edit</t>
+  </si>
+  <si>
+    <t>NINING SUMARNI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4d5d1933-8a53-40f2-bdbd-5939b17e9844/edit</t>
+  </si>
+  <si>
+    <t>JUNG FIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/47dd2d11-ac1a-42ec-9bf9-e21ed1257161/edit</t>
+  </si>
+  <si>
+    <t>NABILA AMARTYA INSANI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8db95f77-ec78-4e50-aa8a-40d845bfe8d0/edit</t>
+  </si>
+  <si>
+    <t>MAHENDRA FAIZ WIRATAMA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c7cb5248-c325-4348-ac25-b0e18a0d1630/edit</t>
+  </si>
+  <si>
+    <t>GUNTUR ALDIANSYAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9a2be78f-0196-4cb3-a6b5-c0aad46945ad/edit</t>
+  </si>
+  <si>
+    <t>WANDI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b9ad5943-dc97-47ba-81bf-8c0eddf53ad1/edit</t>
+  </si>
+  <si>
+    <t>SUCIPTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c64ff48d-381d-40b1-9792-6d6c813ffbbb/edit</t>
+  </si>
+  <si>
+    <t>RIAN PURWANTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7f8e4fdb-3572-4bf4-be26-208d3e3eeb53/edit</t>
+  </si>
+  <si>
+    <t>SUMINAH</t>
+  </si>
+  <si>
+    <t>INAR</t>
+  </si>
+  <si>
+    <t>MISELIA ANGGUN SAPUTRI</t>
+  </si>
+  <si>
+    <t>FITRI MINANTI</t>
+  </si>
+  <si>
+    <t>Ririn Nofianti</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/662c1dd7-53de-484c-804b-9ae21f8e9343/edit</t>
+  </si>
+  <si>
+    <t>FRISKA ARNIA FITRIANI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7bc40858-4902-408d-b497-8fafea5cf998/edit</t>
+  </si>
+  <si>
+    <t>NANDA MAHARANI</t>
+  </si>
+  <si>
+    <t>Zaura Ramadhani</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9fb4db2d-1081-4a9d-b772-b87dc5fcaf8e/edit</t>
+  </si>
+  <si>
+    <t>ADRIANUS AWI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b320b761-fa32-4c23-9321-6ba57403c894/edit</t>
+  </si>
+  <si>
+    <t>WAHYU SABATON</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/95435608-aa43-4e8f-9a19-3069b7079f82/edit</t>
+  </si>
+  <si>
+    <t>BENIDIKTA BENG</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/3745841c-8fae-41ce-8117-8944512aa4e3/edit</t>
+  </si>
+  <si>
+    <t>LIBERTIANUS HERONIMUS HAYKAL</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/0a58cacc-02f5-451e-b8e5-9349a7a9ece1/edit</t>
+  </si>
+  <si>
+    <t>ROSALINA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7869721e-55c6-4af5-9fa0-2f37e37a7843/edit</t>
+  </si>
+  <si>
+    <t>KATARINA RIANTI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/e7b57f04-953c-41f6-a4b1-342914113dd7/edit</t>
+  </si>
+  <si>
+    <t>AGNAYA ZEFANYA PUTRI ANTONIUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/ffe376e3-a4ec-45bc-a4ce-dbc15f857dce/edit</t>
+  </si>
+  <si>
+    <t>ERNIATI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9eaa2755-857a-4722-8dab-20e2fa069bc8/edit</t>
+  </si>
+  <si>
+    <t>ASONG POLAO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/985fd8c6-61cd-49c4-bde4-57e172ee3dba/edit</t>
+  </si>
+  <si>
+    <t>KAMSONSIUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7c6654f3-47aa-4818-9d94-d39724ffbd4d/edit</t>
+  </si>
+  <si>
+    <t>STEFANUS HASAN BASRI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/3d836c1a-105d-421b-9299-af04ace95bee/edit</t>
+  </si>
+  <si>
+    <t>PAULUS INDRA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5441cabd-927d-4734-a9fe-034c048b41b9/edit</t>
+  </si>
+  <si>
+    <t>ANTONIUS NOPO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/d7fbe530-0fad-4d9a-8bfa-3cca8ed0ea42/edit</t>
+  </si>
+  <si>
+    <t>VINSENSIUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/750a3060-f1aa-4b13-a095-17921ca20f78/edit</t>
+  </si>
+  <si>
+    <t>Taufiq hidayahtullah</t>
+  </si>
+  <si>
+    <t>ANGGA SAPUTRA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/f6c4f28e-3bd9-41af-847c-34b75a52ff0e/edit</t>
+  </si>
+  <si>
+    <t>YULIANA AKIAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/f4ee6c6f-e7ae-4fe1-b1ad-4d3a89bd624e/edit</t>
+  </si>
+  <si>
+    <t>YOSEPHA ITA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/6f242cfc-1d99-448a-b6ad-713eba538cf2/edit</t>
+  </si>
+  <si>
+    <t>LODIA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/21b85718-0eb8-4cb7-b218-c310816caebd/edit</t>
+  </si>
+  <si>
+    <t>PETRUS EKO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4ad18eb3-0949-4861-9ac8-0af723292850/edit</t>
+  </si>
+  <si>
+    <t>ANASTASIA RATNA ANGGINI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/928b9be9-a938-4457-93c3-ba5f815923c2/edit</t>
+  </si>
+  <si>
+    <t>TERESIA ASISKA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/59dec34d-8797-4ff0-a371-325de58c8197/edit</t>
+  </si>
+  <si>
+    <t>BLASIUS RIVAI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/604e4700-a369-46df-ab72-5893c9fdb676/edit</t>
+  </si>
+  <si>
+    <t>FEBRIAN REVAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/befa5dd7-d886-494e-a318-1bdbc932aa60/edit</t>
+  </si>
+  <si>
+    <t>ARIP</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b8b3038b-3aae-457d-9677-93d81cfac3c6/edit</t>
+  </si>
+  <si>
+    <t>PIANUS AKI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b8b11693-2d1e-49e9-94fe-f896a4349edd/edit</t>
+  </si>
+  <si>
+    <t>Atian jelsi</t>
+  </si>
+  <si>
+    <t>PATMAWATI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/35177883-f636-4e62-ae22-a509ac8d772e/edit</t>
+  </si>
+  <si>
+    <t>DIUN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/95007dc0-f180-4392-965e-717597ec9b61/edit</t>
+  </si>
+  <si>
+    <t>EVI MELLIANTI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/e6bcc25d-6305-46e2-95d9-849c05cd9ae4/edit</t>
+  </si>
+  <si>
+    <t>Auliya putri rezokiya</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/d3ce548f-4ddb-4afa-95a1-63c7eaa869a9/edit</t>
+  </si>
+  <si>
+    <t>Kelsi Margaret</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/1aeb7ba2-3a37-4056-a690-45f0f465a81e/edit</t>
+  </si>
+  <si>
+    <t>SILVANUS LIPUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5e4cef07-655b-406e-a61e-cb7bc2ff36b3/edit</t>
+  </si>
+  <si>
+    <t>YOHANA JOT</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/48e742de-dc99-4e29-930b-cda62c8b006d/edit</t>
+  </si>
+  <si>
+    <t>ALYA FITRIANI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/449520ab-fbb9-48fa-905c-eca3f443a563/edit</t>
+  </si>
+  <si>
+    <t>Herkulanus fery</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7bd25ca3-b25f-4b9e-b8bd-6dd42c483831/edit</t>
+  </si>
+  <si>
+    <t>GODEFRIDUS FERLANG ALFEUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/eb3707ec-85e5-43eb-b101-ee351ba0aa44/edit</t>
+  </si>
+  <si>
+    <t>POLI HASADUNGAN SIMANJUNTAK</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/363d725f-51cb-451d-8c9f-0661643d8402/edit</t>
+  </si>
+  <si>
+    <t>PANAHATAN SINURAT</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8e54dee3-4c24-4fd0-b4e2-fb6a01f493fd/edit</t>
+  </si>
+  <si>
+    <t>BELI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7166d643-fabe-4228-8f45-8f5d714dda0e/edit</t>
+  </si>
+  <si>
+    <t>TAYAK</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7c78574d-8ec9-42f2-bb4b-9cb9cf26857e/edit</t>
+  </si>
+  <si>
+    <t>NATALI GREYSTIA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/98966a2b-2f59-4645-94ed-d0a6b2db4122/edit</t>
+  </si>
+  <si>
+    <t>SABINUS RUDIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/dc38001b-1796-444a-8ac8-0b26f57132f8/edit</t>
+  </si>
+  <si>
+    <t>INDRA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/829c174c-1684-427a-84f3-21d0f3953d75/edit</t>
+  </si>
+  <si>
+    <t>ABEL AWALI BRODUS</t>
+  </si>
+  <si>
+    <t>FLOREN TINUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7be4d75d-4084-4da0-90c5-a49f6313bf28/edit</t>
+  </si>
+  <si>
+    <t>SUPRIYADI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8ac51344-908a-4333-aa02-4aca7f100b09/edit</t>
+  </si>
+  <si>
+    <t>MAWA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b43e3fac-bfef-457d-bb07-0965ec3cb418/edit</t>
+  </si>
+  <si>
+    <t>THEODOR IMMANUEL</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/f7802cb6-15fd-4b19-a0a1-c04962e33b42/edit</t>
+  </si>
+  <si>
+    <t>EDI SUHARDI</t>
+  </si>
+  <si>
+    <t>YEREMIAS SUPARNO</t>
+  </si>
+  <si>
+    <t>LINDA LESTARI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5d0f4a7f-35c9-4fbb-a7d6-61e5b761628c/edit</t>
+  </si>
+  <si>
+    <t>Valeria kristin</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/bc3c6e34-0cfc-4107-b221-215e99065aa0/edit</t>
+  </si>
+  <si>
+    <t>JINIARTI NOBERTA ROSALIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5947700b-4d5a-440c-b13a-152095282cec/edit</t>
+  </si>
+  <si>
+    <t>YOHANA RAPINA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a29a8035-0550-4f5b-bdd5-1ab58851384d/edit</t>
+  </si>
+  <si>
+    <t>SERAVINA DESI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/947f3850-f41c-4039-8ead-ba9209348bc6/edit</t>
+  </si>
+  <si>
+    <t>ALVARO GIBRAN JORDAN</t>
+  </si>
+  <si>
+    <t>OKTAVIANUS AJIS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/53402646-dd70-4299-bd5c-cda52fcbf2df/edit</t>
+  </si>
+  <si>
+    <t>DEO PUTRAOKO.GM</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/54eaaff1-0c89-4b66-98f2-880110277d3e/edit</t>
+  </si>
+  <si>
+    <t>WAHYU SETIAWAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/921e7da1-eb4d-474f-981a-613f12d35344/edit</t>
+  </si>
+  <si>
+    <t>TAHIF</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/67643c7a-b7ac-4916-b345-e05a0014f504/edit</t>
+  </si>
+  <si>
+    <t>AGUSTINUS ARIYA DE KAYUWALE</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/768aae45-8992-4366-b82c-11f0d301f8f0/edit</t>
+  </si>
+  <si>
+    <t>IRFAN HILMI NASUTION</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/d4f9e123-1929-4507-951d-5e8d0fec838e/edit</t>
+  </si>
+  <si>
+    <t>ALBERTUS JUJUL</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b6a3a938-7c4c-4958-8449-3596c8b8d8a3/edit</t>
+  </si>
+  <si>
+    <t>Febi anugrah putra</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/2d530772-a129-430f-bd60-ab5c1cac6e5a/edit</t>
+  </si>
+  <si>
+    <t>SAMUEL LABARTA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/576e2b84-6498-4acf-896f-ab812f8ff170/edit</t>
+  </si>
+  <si>
+    <t>ARYA PRATAMA</t>
+  </si>
+  <si>
+    <t>VALENTINO AHO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/76033557-5ddb-47e0-8963-af57bc20918c/edit</t>
+  </si>
+  <si>
+    <t>EFIFANI ERWANDA VARADILLA</t>
+  </si>
+  <si>
+    <t>MULIANA SRI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/df35a563-96d7-43f2-a2fe-afaff32c8805/edit</t>
+  </si>
+  <si>
+    <t>TIYARA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9bad7cf0-0c06-4ec7-b9c2-719a9da0ba9c/edit</t>
+  </si>
+  <si>
+    <t>BENNY IRFANTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/83aa16f9-ca5a-4bdd-afa9-b5de5f632608/edit</t>
+  </si>
+  <si>
+    <t>DANA HERLINA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b5e8493e-793c-4f32-bc94-35426aae6a85/edit</t>
+  </si>
+  <si>
+    <t>PENI SAWALINA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/961824db-86d0-45b6-b21d-04fbd334b991/edit</t>
+  </si>
+  <si>
+    <t>LIM KWET JUNG</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8d046793-8220-448e-bdb0-57bdd19af61e/edit</t>
+  </si>
+  <si>
+    <t>KATARINA LALA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/09991659-c460-45e4-bc53-4086925f5fdd/edit</t>
+  </si>
+  <si>
+    <t>AWALLUDIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5a050eb0-e8f7-4ac2-8c0c-e07f4a4efe61/edit</t>
+  </si>
+  <si>
+    <t>SURATMI</t>
+  </si>
+  <si>
+    <t>FELICIA JUSE</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/145110be-6a78-407d-9d80-10a112468866/edit</t>
+  </si>
+  <si>
+    <t>SLAMET RIYADI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/121147f3-5ccc-48cf-a29f-0c2276e8bbd4/edit</t>
+  </si>
+  <si>
+    <t>AMANDUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/557a2295-5b95-441e-b19c-e425d3a8cf3b/edit</t>
+  </si>
+  <si>
+    <t>ALOYSIUS PURNOMO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7534b50f-eb5c-4ac6-92c6-29720bd58795/edit</t>
+  </si>
+  <si>
+    <t>RIYAN HIDAYAT</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8d9852dd-bd51-4370-85d8-beef6d169df3/edit</t>
+  </si>
+  <si>
+    <t>KARMELUS MIJAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/448eece9-78f1-4b8d-838c-50b74c1900af/edit</t>
+  </si>
+  <si>
+    <t>ERPINUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7236a6eb-be6c-47eb-8db3-3c3a173b6e60/edit</t>
+  </si>
+  <si>
+    <t>KRISTIAN ALPIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7ba5ede7-880d-41a0-8eb2-f89f9939dfe7/edit</t>
+  </si>
+  <si>
+    <t>BAGAS GONZAGA ALDYAPRIDUO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9e6ae1f8-30e0-4021-80f3-dcb79961a312/edit</t>
+  </si>
+  <si>
+    <t>NATALIUS TRIAWAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/43a3742f-4182-49b5-943d-5cc66cc04f51/edit</t>
+  </si>
+  <si>
+    <t>YOSEP. A. G</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/967e9f33-fc49-4393-ad08-695db70fb41c/edit</t>
+  </si>
+  <si>
+    <t>YORDANUS AGUSTIAWAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4ef24cdc-bc48-406d-aece-9b389dd64b0a/edit</t>
+  </si>
+  <si>
+    <t>ANTONY</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5ac698ca-3f37-46f8-a5e2-6f2228a24638/edit</t>
+  </si>
+  <si>
+    <t>MIGUEL HARVEY ARSENIO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c02e4cc2-6e4b-496b-8401-2c49a3a90ffd/edit</t>
+  </si>
+  <si>
+    <t>PITRONIUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/99f367a2-ac2a-47b5-9c4e-d0f7fc10424c/edit</t>
+  </si>
+  <si>
+    <t>HILARIUS RISWAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8afaf86d-588b-4635-858f-1dad5965d046/edit</t>
+  </si>
+  <si>
+    <t>Nurhayati</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/fa11c3cc-0fce-4a0f-ba9e-d55cbabe2888/edit</t>
+  </si>
+  <si>
+    <t>LIDIA AROK</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8e0a6a7e-184a-47a1-8199-69a3e9788441/edit</t>
+  </si>
+  <si>
+    <t>JULIANA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/46cfe057-ec41-4278-96f8-78fb0eb05775/edit</t>
+  </si>
+  <si>
+    <t>OLIPIA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/73d59b34-3804-4a9e-8aad-ccf148fd7f3c/edit</t>
+  </si>
+  <si>
+    <t>ROCHAIDAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/e5804ce4-e62f-4b37-807e-d50aa0a69465/edit</t>
+  </si>
+  <si>
+    <t>OKTAVIANUS CHRIS KARIANTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9c918058-1fba-4ef6-af92-ab129c11ea0a/edit</t>
+  </si>
+  <si>
+    <t>BRIGIDA FELACITA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/38c9bef6-f1bc-45d9-a0e2-39dfd8e81cb9/edit</t>
+  </si>
+  <si>
+    <t>JHON NOPEBRIAN KELVIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8a70c531-4d75-4bf1-b5b1-e6cfd63622c8/edit</t>
+  </si>
+  <si>
+    <t>RISMA SANTIKA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8c27d644-2c0f-4bcb-8370-9a53ee5b33ae/edit</t>
+  </si>
+  <si>
+    <t>SIRUS SUANDI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/681364ba-7a81-4f68-a453-20686386bd94/edit</t>
+  </si>
+  <si>
+    <t>RIA RIASVALENA</t>
+  </si>
+  <si>
+    <t>FLORETTA ZEA ARETHA</t>
+  </si>
+  <si>
+    <t>Sisilia Fani</t>
+  </si>
+  <si>
+    <t>FRANSISKA SELIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/e02d3a5a-56a2-4fb4-a03f-8361073beead/edit</t>
+  </si>
+  <si>
+    <t>SELUTUNG</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b76d41a1-d20b-413f-8eb1-3dff1ccc0d0d/edit</t>
+  </si>
+  <si>
+    <t>EKOLIMUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7f25d878-59b8-4730-a743-dc2141643359/edit</t>
+  </si>
+  <si>
+    <t>JULIANUS IRVAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b15c95ab-1d81-4e90-adfd-a8ca6f77067b/edit</t>
+  </si>
+  <si>
+    <t>HENDRIKUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a6b6a2ab-f05d-4843-b6e1-85446ead77c5/edit</t>
+  </si>
+  <si>
+    <t>HENDRIKUS EEN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/95f18264-c20e-45f6-87e0-3ba1c6d6a1b5/edit</t>
+  </si>
+  <si>
+    <t>HERVAN.</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/ab495bf6-6f39-4179-871b-be6e0b4769aa/edit</t>
+  </si>
+  <si>
+    <t>RAFAEL DWI ARYAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/afa678e1-91f1-4e93-bf21-f29e41b5da6a/edit</t>
+  </si>
+  <si>
+    <t>ANDIKA PRATAMA</t>
+  </si>
+  <si>
+    <t>PAUSTINUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/3d794e6a-fa21-4727-8d7f-c34dc24e4002/edit</t>
+  </si>
+  <si>
+    <t>ANDRIA SAPUTRA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/655b850c-7233-4bd6-b621-2d18f623335c/edit</t>
+  </si>
+  <si>
+    <t>HAMDANI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/365de131-0cf0-49c5-ab86-059f79672b1d/edit</t>
+  </si>
+  <si>
+    <t>DEWI RATNALIASARI</t>
+  </si>
+  <si>
+    <t>Alyka putri</t>
+  </si>
+  <si>
+    <t>SURYANTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/6ce88c59-a026-4a50-b1c9-ff099e757972/edit</t>
+  </si>
+  <si>
+    <t>DARE</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/37c320b3-99d2-4f5c-9061-fcc635d73f50/edit</t>
+  </si>
+  <si>
+    <t>RUBENSONO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a3cd3197-c626-4eac-bfbe-cce9fa66f075/edit</t>
+  </si>
+  <si>
+    <t>MARIANA MEILEN</t>
+  </si>
+  <si>
+    <t>EKA MULTI ODRIYANI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a1b45377-e9d0-4c1a-b01d-fe7e41aa80f2/edit</t>
+  </si>
+  <si>
+    <t>DEVI STEVANI HILLERIA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/94fc3cb1-64ec-4fa4-a335-3589da978372/edit</t>
+  </si>
+  <si>
+    <t>NUR ALIMAH</t>
+  </si>
+  <si>
+    <t>ELKLESYA MALAICHA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/ea0133b5-5c23-436d-9e28-3809d0f5434a/edit</t>
+  </si>
+  <si>
+    <t>MARIA DESI JUNIARTI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c3e9b0cd-fbfe-4731-8e6a-9447bd613fb6/edit</t>
+  </si>
+  <si>
+    <t>ANEM</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/51d2c6db-7820-4dfd-94fc-6f0b21253135/edit</t>
+  </si>
+  <si>
+    <t>ROMINU IKA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/3b6c5200-2640-459c-bff7-831bbaede02c/edit</t>
+  </si>
+  <si>
+    <t>WAN HENDRIK</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/87cc3bde-9b34-4cac-a7ed-a85dc2e7873e/edit</t>
+  </si>
+  <si>
+    <t>RAFI DERBIANSYAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/781a48d3-a05c-427c-aa6c-f31c89eed160/edit</t>
+  </si>
+  <si>
+    <t>MUHAMMAD KHAIRIL AL HABSYI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8de0dbf0-14fd-48b4-b30f-d1ffc14a19d5/edit</t>
+  </si>
+  <si>
+    <t>ANDREAS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/faea56ae-8840-407b-99f7-9886543c6e65/edit</t>
+  </si>
+  <si>
+    <t>GUSNIARTI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/768d5506-8169-4396-ad69-986227c78a30/edit</t>
+  </si>
+  <si>
+    <t>GEORGIUS ZENO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/69e1b731-8409-42e2-87f0-f3a3b761abd8/edit</t>
+  </si>
+  <si>
+    <t>ANTONIUS JEEP</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8a58601f-335f-4b2a-9005-2d501354feeb/edit</t>
+  </si>
+  <si>
+    <t>DJARNO BASOEKI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/936544fe-d49e-430d-b490-2243ba5e0917/edit</t>
+  </si>
+  <si>
+    <t>ALTHAF ABIZAR</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5330bbab-1b38-425c-8ba6-740c91d23840/edit</t>
+  </si>
+  <si>
+    <t>STIVEN ARDI PUTAPAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4a905a2b-9123-40cb-8c36-aec64c3bf8d0/edit</t>
+  </si>
+  <si>
+    <t>ALFA ALTHARIQ QALBIKA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/dd7a4934-4fdc-4c06-a0ea-8a0e5143ec38/edit</t>
+  </si>
+  <si>
+    <t>TEODULUS SATRIO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c91d8881-b8cd-4231-a05a-d19c04d20faf/edit</t>
+  </si>
+  <si>
+    <t>KRISTIAN JONATAN</t>
+  </si>
+  <si>
+    <t>RAMIADI KURNIAWAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/e7ac1d86-5ac2-4ae6-8701-daa1dd1fc347/edit</t>
+  </si>
+  <si>
+    <t>SYAMSUL BACHRI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/81473ac0-8698-438d-b489-652adbc6970d/edit</t>
+  </si>
+  <si>
+    <t>NIKKY ARTA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/66cb3010-2f39-426b-bfd3-63b0055d35c4/edit</t>
+  </si>
+  <si>
+    <t>AKIM</t>
+  </si>
+  <si>
+    <t>REYSHA AQEILA KURNIATI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8ca64f8c-92da-45ab-87cb-043102a666a5/edit</t>
+  </si>
+  <si>
+    <t>Mutia putri</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/3ffd89fb-5a06-4792-bcf0-029c031cf1e6/edit</t>
+  </si>
+  <si>
+    <t>KIN LUK</t>
+  </si>
+  <si>
+    <t>ACIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/befa64f5-8e3b-4a2e-ae18-29ff30523fc0/edit</t>
+  </si>
+  <si>
+    <t>THEN SIAT KHIN</t>
+  </si>
+  <si>
+    <t>AGUNG ELDA MARIS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/438c45ce-e9cd-4037-8709-58ee06bc2acf/edit</t>
+  </si>
+  <si>
+    <t>SINAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c0cb1060-0976-47ae-bcb5-a5d1867a1601/edit</t>
+  </si>
+  <si>
+    <t>KWET FI</t>
+  </si>
+  <si>
+    <t>YENNI OKTAVIA FRANSISKA</t>
+  </si>
+  <si>
+    <t>AINUN MIFTAHUL JANNNAH</t>
+  </si>
+  <si>
+    <t>MILAWATI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/379e8003-3b3e-4994-ae29-b618c6dce671/edit</t>
+  </si>
+  <si>
+    <t>AGUS PARLAN BUDIANTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b25b6fff-0c0e-43a5-bc2e-2c685c4bd46b/edit</t>
+  </si>
+  <si>
+    <t>JULIANTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c4bcf85b-d7b4-4f91-8992-bf21a654e089/edit</t>
+  </si>
+  <si>
+    <t>VINSENSIUS EKO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/82844308-0d65-4132-a247-44ca024547f7/edit</t>
+  </si>
+  <si>
+    <t>MARTA FINA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/6a2d7485-4cbf-4019-8bac-b706fddb6efa/edit</t>
+  </si>
+  <si>
+    <t>LUSIANA CURENG</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/96f0f1c6-3cee-4ab6-8517-2fe2e4315e76/edit</t>
+  </si>
+  <si>
+    <t>PURWADI</t>
+  </si>
+  <si>
+    <t>SILANG</t>
+  </si>
+  <si>
+    <t>Sentia</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/aecb43f8-e7ec-4499-8591-7cbf0784040b/edit</t>
+  </si>
+  <si>
+    <t>Lora pitronila</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/70c1170d-946a-4fa6-b050-54aa0901e3bb/edit</t>
+  </si>
+  <si>
+    <t>JOAN PENGHARAPAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a244fc13-186b-4abe-80bf-ef7e908e966b/edit</t>
+  </si>
+  <si>
+    <t>FITRIANA ARNIAWATI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7dba61fa-c6a1-41ee-b800-e77983b84e65/edit</t>
+  </si>
+  <si>
+    <t>ALYANSIUS RISANDA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/abbeb860-e3c5-44b5-9340-fbd511595657/edit</t>
+  </si>
+  <si>
+    <t>HARIYANTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7b2c21bb-8994-43a5-b3e3-531aa77e9b46/edit</t>
+  </si>
+  <si>
+    <t>VINANSIUS OLLA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4db9ffa2-7aa6-4e04-9856-3779b381b0d3/edit</t>
+  </si>
+  <si>
+    <t>GERADUS BAET</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/34d7e9b8-031a-4f99-a1f7-c2571350c401/edit</t>
+  </si>
+  <si>
+    <t>KRISTINA EMELIA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a32d0df5-dcd2-499d-ab02-6f3dadf49ea5/edit</t>
+  </si>
+  <si>
+    <t>ANASTASIA</t>
+  </si>
+  <si>
+    <t>KATARINA CARA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/73afde75-a24e-4333-9bbb-8e98f484328c/edit</t>
+  </si>
+  <si>
+    <t>YULIANA TITIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/852b1873-dffc-4a0a-8ad2-a4409f56d73e/edit</t>
+  </si>
+  <si>
+    <t>ADIT</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/90a03705-eace-4bfe-8a51-fd727c07edb9/edit</t>
+  </si>
+  <si>
+    <t>STEVAN YORANDA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4d5e6ae0-1fa3-42de-b606-7c279b379422/edit</t>
+  </si>
+  <si>
+    <t>ARMAN FEBRIANSYAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/59471161-5355-48d2-8199-1d163afa49e0/edit</t>
+  </si>
+  <si>
+    <t>JUPANI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/450af2ca-4224-4390-a73a-08a31daaa9d5/edit</t>
+  </si>
+  <si>
+    <t>ABDULLAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7441e406-1c58-41b7-a02a-abe78b89769f/edit</t>
+  </si>
+  <si>
+    <t>IQBAL HANIF ANGGARA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5e3a4aba-7f74-4ad2-949f-f279f8e7f417/edit</t>
+  </si>
+  <si>
+    <t>SUDARMAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a3b3dac2-2960-47c2-8040-709e2c3236e4/edit</t>
+  </si>
+  <si>
+    <t>APIN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/2da5e46d-26db-4408-93ba-cc28153613f6/edit</t>
+  </si>
+  <si>
+    <t>DENNY VERIADI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/a97af458-857d-462c-b189-0bc00ffbbff4/edit</t>
+  </si>
+  <si>
+    <t>HIRAWAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7d10ec16-be27-4f4e-ba30-57bd775c434a/edit</t>
+  </si>
+  <si>
+    <t>AAN HAIRUL</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4794e0d9-b3a1-461b-acbb-ebf37c0174e9/edit</t>
+  </si>
+  <si>
+    <t>ANO NITIS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b9e2d24b-79a3-48b3-aaab-cd56a237e00f/edit</t>
+  </si>
+  <si>
+    <t>DOMINIKUS KHAM</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9aa3ae95-221f-484a-9558-794725e01ca2/edit</t>
+  </si>
+  <si>
+    <t>AGUSTIAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7a6949a0-f6f0-44d2-9081-e4588139b5e6/edit</t>
+  </si>
+  <si>
+    <t>MARSELINUS</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/2cea4785-25ae-4ed0-ad60-14fefcd62e3a/edit</t>
+  </si>
+  <si>
+    <t>HARYANTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/91d3921f-fc74-4205-af9e-d94d2d4efb8b/edit</t>
+  </si>
+  <si>
+    <t>RAHMAD HERI PURNOMO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b82dd90b-5843-4950-9a54-34d048420f72/edit</t>
+  </si>
+  <si>
+    <t>INDRA SETIYAWAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/51a3bca2-a2d7-409f-b967-67b91a0b99e4/edit</t>
+  </si>
+  <si>
+    <t>RIAN ARIF PRATAMA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/915a76b4-cdd5-45a3-924b-e218129262fd/edit</t>
+  </si>
+  <si>
+    <t>Syahibunawar</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c0162c40-95aa-49fb-88c6-90d13b8d3f4c/edit</t>
+  </si>
+  <si>
+    <t>JOKO PURWANTO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/3b16ecb2-c2bf-4378-af79-b95fba8a53bf/edit</t>
+  </si>
+  <si>
+    <t>SUMARJI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/49d6cfcd-45fc-4e73-baaa-6118727dfc0f/edit</t>
+  </si>
+  <si>
+    <t>NATA KUSUMA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7e064db1-628b-4ac7-8edf-22164f907cd8/edit</t>
+  </si>
+  <si>
+    <t>SUKINO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/58d513ce-a93e-482a-8b45-a5c65693c740/edit</t>
+  </si>
+  <si>
+    <t>POLENI TIKA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/91e717fd-80b2-4913-b505-d4284218e6c5/edit</t>
+  </si>
+  <si>
+    <t>LIPONG</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/6b539154-3dd3-4d13-8bcb-a23a18818881/edit</t>
+  </si>
+  <si>
+    <t>ARSYILA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8e9c4daf-4eb6-427c-9d13-9b40c83d8de8/edit</t>
+  </si>
+  <si>
+    <t>LUSIA DWIYATI. C</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/712d93cf-0ef3-4ec1-b055-56c90dce3102/edit</t>
+  </si>
+  <si>
+    <t>Atik susilawati</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5ff803a5-153e-43fd-8a06-3baaf3aa2682/edit</t>
+  </si>
+  <si>
+    <t>ARIYATNO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/90e42c6d-5d22-4a89-a5e8-62b53bf1a491/edit</t>
+  </si>
+  <si>
+    <t>HERKULANUS PANDI</t>
+  </si>
+  <si>
+    <t>ASENAH</t>
+  </si>
+  <si>
+    <t>SRI WAHYUNI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/751c8cc4-24ae-4921-a93c-e06c639cf90b/edit</t>
+  </si>
+  <si>
+    <t>LIE SUI SAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/58c088da-722f-427c-b7aa-1aca97dedc0c/edit</t>
+  </si>
+  <si>
+    <t>LATEH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/5a8ef6a1-54b3-428c-9b0d-b7c16ba7ed05/edit</t>
+  </si>
+  <si>
+    <t>Wili widya</t>
+  </si>
+  <si>
+    <t>KAYLA ALMAIRA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b4f21022-dcb4-4d93-8dbb-fd24e60f48a7/edit</t>
+  </si>
+  <si>
+    <t>MARIA ANGGRAINI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/67a4e9c6-1157-46b3-859f-0d8707830f3f/edit</t>
+  </si>
+  <si>
+    <t>NIA JULFIANTI</t>
+  </si>
+  <si>
+    <t>MAYA PUSPITA SARI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b28f6462-8cb7-4140-bb19-4cec7f88b409/edit</t>
+  </si>
+  <si>
+    <t>ANASTASIA YUNI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c70b80a3-beb0-4b4a-b3e6-e1ce56bb64b0/edit</t>
+  </si>
+  <si>
+    <t>SOCHIBUN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/48b88994-00ab-4bd1-b3f7-73b620991fe1/edit</t>
+  </si>
+  <si>
+    <t>EKA ERNAWATI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b7dcb7f2-e9df-447e-a5df-0ce9d3b282bb/edit</t>
+  </si>
+  <si>
+    <t>RUBIYEM</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/dd756a2f-6705-4c86-8a96-b00901cac446/edit</t>
+  </si>
+  <si>
+    <t>DINDA</t>
+  </si>
+  <si>
+    <t>FITRIANI</t>
+  </si>
+  <si>
+    <t>DEVITA NATALIA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/c3741259-24a5-46ed-835a-75642d7038ef/edit</t>
+  </si>
+  <si>
+    <t>TEYA AVRILIA</t>
+  </si>
+  <si>
+    <t>JELITA GABRIELA</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/4f2b589f-048b-4c5b-8dad-fbacc590acce/edit</t>
+  </si>
+  <si>
+    <t>ALFI DWI NURSAPUTRI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/9b8406e1-06f7-4b4f-88dc-af8ec74961aa/edit</t>
+  </si>
+  <si>
+    <t>DONNY SEMBIRING</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/417c283d-8cb3-4a61-bba5-38ffab00267e/edit</t>
+  </si>
+  <si>
+    <t>RAYMANDUS KLEMEN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/8e2332d2-6b88-440a-baa0-6deefdc715d7/edit</t>
+  </si>
+  <si>
+    <t>ARDZA FADILAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7c3fb560-4d2d-492d-a521-0dab1eae159b/edit</t>
+  </si>
+  <si>
+    <t>ALYA SYAFIQHA PUTRI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/262e6373-9517-4ba2-bd15-a839bdcc8c4e/edit</t>
+  </si>
+  <si>
+    <t>WAHYU SULESTRIYONO</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b7a66eb2-a647-4ff5-8a71-49daa8b493db/edit</t>
+  </si>
+  <si>
+    <t>PUTRI INTAN SARI</t>
+  </si>
+  <si>
+    <t>Neliyana</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/24d79a65-b5a7-4391-8c3c-cdab56e0cf3d/edit</t>
+  </si>
+  <si>
+    <t>TONI</t>
+  </si>
+  <si>
+    <t>FIRDAUS ALKADRI</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/93dc16f0-4d08-4996-914d-49c6c78a0460/edit</t>
+  </si>
+  <si>
+    <t>MUHAMMAD IKHSAN</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/69682498-22e8-4985-b032-df43965f6b65/edit</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/b5626502-5c48-488f-8f18-54dbb85cd5d6/edit</t>
+  </si>
+  <si>
+    <t>DZAKIYYAH MUFIDAH</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/fccfa0e6-0187-4a4e-acc9-57232459e3f1/edit</t>
+  </si>
+  <si>
+    <t>Nata ria halim</t>
+  </si>
+  <si>
+    <t>https://fasih-sm.bps.go.id/app/assignment/fd68e454-ba45-4b85-8205-f3bf777ded24/7d902eb7-44ac-49e2-a772-71eb00fbf0bc/edit</t>
+  </si>
+  <si>
+    <t>ARIS DARWOKO</t>
   </si>
 </sst>
 </file>
@@ -81,14 +1902,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,28 +2365,31 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -581,121 +2398,118 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1047,8 +2861,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:D341"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -1080,10 +2894,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
@@ -1094,10 +2908,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -1108,10 +2922,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -1122,15 +2936,4705 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>47</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>120</v>
+      </c>
+      <c r="B64" t="s">
+        <v>121</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>122</v>
+      </c>
+      <c r="B65" t="s">
+        <v>123</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" t="s">
+        <v>124</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>125</v>
+      </c>
+      <c r="B67" t="s">
+        <v>126</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" t="s">
+        <v>130</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>120</v>
+      </c>
+      <c r="B71" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>132</v>
+      </c>
+      <c r="B72" t="s">
+        <v>133</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>31</v>
+      </c>
+      <c r="B73" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>137</v>
+      </c>
+      <c r="B75" t="s">
+        <v>138</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" t="s">
+        <v>139</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>140</v>
+      </c>
+      <c r="B77" t="s">
+        <v>141</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B78" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>144</v>
+      </c>
+      <c r="B79" t="s">
+        <v>145</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>146</v>
+      </c>
+      <c r="B80" t="s">
+        <v>147</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>148</v>
+      </c>
+      <c r="B81" t="s">
+        <v>149</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" t="s">
+        <v>151</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>152</v>
+      </c>
+      <c r="B83" t="s">
+        <v>153</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" t="s">
+        <v>155</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>156</v>
+      </c>
+      <c r="B85" t="s">
+        <v>157</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>158</v>
+      </c>
+      <c r="B86" t="s">
+        <v>159</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>160</v>
+      </c>
+      <c r="B87" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>154</v>
+      </c>
+      <c r="B88" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D88" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>150</v>
+      </c>
+      <c r="B89" t="s">
+        <v>163</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>160</v>
+      </c>
+      <c r="B90" t="s">
+        <v>164</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>17</v>
+      </c>
+      <c r="B91" t="s">
+        <v>165</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>166</v>
+      </c>
+      <c r="B92" t="s">
+        <v>167</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>168</v>
+      </c>
+      <c r="B93" t="s">
+        <v>169</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D93" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>17</v>
+      </c>
+      <c r="B94" t="s">
+        <v>170</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>171</v>
+      </c>
+      <c r="B95" t="s">
+        <v>172</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>173</v>
+      </c>
+      <c r="B96" t="s">
+        <v>174</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>175</v>
+      </c>
+      <c r="B97" t="s">
+        <v>176</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>177</v>
+      </c>
+      <c r="B98" t="s">
+        <v>178</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>179</v>
+      </c>
+      <c r="B99" t="s">
+        <v>180</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>181</v>
+      </c>
+      <c r="B100" t="s">
+        <v>182</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>183</v>
+      </c>
+      <c r="B101" t="s">
+        <v>184</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>185</v>
+      </c>
+      <c r="B102" t="s">
+        <v>186</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>187</v>
+      </c>
+      <c r="B103" t="s">
+        <v>188</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>189</v>
+      </c>
+      <c r="B104" t="s">
+        <v>190</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>191</v>
+      </c>
+      <c r="B105" t="s">
+        <v>192</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>193</v>
+      </c>
+      <c r="B106" t="s">
+        <v>194</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>195</v>
+      </c>
+      <c r="B107" t="s">
+        <v>196</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>197</v>
+      </c>
+      <c r="B108" t="s">
+        <v>198</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D108" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>199</v>
+      </c>
+      <c r="B109" t="s">
+        <v>200</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D109" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>187</v>
+      </c>
+      <c r="B110" t="s">
+        <v>201</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>202</v>
+      </c>
+      <c r="B111" t="s">
+        <v>203</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>204</v>
+      </c>
+      <c r="B112" t="s">
+        <v>205</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D112" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>206</v>
+      </c>
+      <c r="B113" t="s">
+        <v>207</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D113" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>187</v>
+      </c>
+      <c r="B114" t="s">
+        <v>188</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D114" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>208</v>
+      </c>
+      <c r="B115" t="s">
+        <v>209</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>210</v>
+      </c>
+      <c r="B116" t="s">
+        <v>211</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D116" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>212</v>
+      </c>
+      <c r="B117" t="s">
+        <v>213</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D117" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>214</v>
+      </c>
+      <c r="B118" t="s">
+        <v>215</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D118" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
+        <v>216</v>
+      </c>
+      <c r="B119" t="s">
+        <v>217</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D119" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
+        <v>218</v>
+      </c>
+      <c r="B120" t="s">
+        <v>219</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
+        <v>220</v>
+      </c>
+      <c r="B121" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D121" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
+        <v>222</v>
+      </c>
+      <c r="B122" t="s">
+        <v>223</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D122" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>218</v>
+      </c>
+      <c r="B123" t="s">
+        <v>224</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D123" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
+        <v>225</v>
+      </c>
+      <c r="B124" t="s">
+        <v>226</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D124" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>227</v>
+      </c>
+      <c r="B125" t="s">
+        <v>228</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D125" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>229</v>
+      </c>
+      <c r="B126" t="s">
+        <v>230</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D126" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>231</v>
+      </c>
+      <c r="B127" t="s">
+        <v>232</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D127" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
+        <v>233</v>
+      </c>
+      <c r="B128" t="s">
+        <v>234</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>235</v>
+      </c>
+      <c r="B129" t="s">
+        <v>236</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D129" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>237</v>
+      </c>
+      <c r="B130" t="s">
+        <v>238</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D130" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>239</v>
+      </c>
+      <c r="B131" t="s">
+        <v>240</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D131" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>241</v>
+      </c>
+      <c r="B132" t="s">
+        <v>242</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D132" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>243</v>
+      </c>
+      <c r="B133" t="s">
+        <v>244</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D133" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>245</v>
+      </c>
+      <c r="B134" t="s">
+        <v>246</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D134" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
+        <v>247</v>
+      </c>
+      <c r="B135" t="s">
+        <v>248</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
+        <v>249</v>
+      </c>
+      <c r="B136" t="s">
+        <v>250</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D136" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
+        <v>251</v>
+      </c>
+      <c r="B137" t="s">
+        <v>252</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
+        <v>253</v>
+      </c>
+      <c r="B138" t="s">
+        <v>254</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D138" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
+        <v>255</v>
+      </c>
+      <c r="B139" t="s">
+        <v>256</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D139" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
+        <v>257</v>
+      </c>
+      <c r="B140" t="s">
+        <v>258</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D140" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
+        <v>253</v>
+      </c>
+      <c r="B141" t="s">
+        <v>259</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D141" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
+        <v>260</v>
+      </c>
+      <c r="B142" t="s">
+        <v>261</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D142" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
+        <v>262</v>
+      </c>
+      <c r="B143" t="s">
+        <v>263</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D143" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" t="s">
+        <v>264</v>
+      </c>
+      <c r="B144" t="s">
+        <v>265</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D144" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" t="s">
+        <v>266</v>
+      </c>
+      <c r="B145" t="s">
+        <v>267</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D145" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" t="s">
+        <v>253</v>
+      </c>
+      <c r="B146" t="s">
+        <v>268</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" t="s">
+        <v>251</v>
+      </c>
+      <c r="B147" t="s">
+        <v>269</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D147" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" t="s">
+        <v>270</v>
+      </c>
+      <c r="B148" t="s">
+        <v>271</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D148" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" t="s">
+        <v>272</v>
+      </c>
+      <c r="B149" t="s">
+        <v>273</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D149" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" t="s">
+        <v>274</v>
+      </c>
+      <c r="B150" t="s">
+        <v>275</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D150" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" t="s">
+        <v>276</v>
+      </c>
+      <c r="B151" t="s">
+        <v>277</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D151" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" t="s">
+        <v>278</v>
+      </c>
+      <c r="B152" t="s">
+        <v>279</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D152" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" t="s">
+        <v>272</v>
+      </c>
+      <c r="B153" t="s">
+        <v>280</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D153" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" t="s">
+        <v>281</v>
+      </c>
+      <c r="B154" t="s">
+        <v>282</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D154" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" t="s">
+        <v>283</v>
+      </c>
+      <c r="B155" t="s">
+        <v>284</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D155" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" t="s">
+        <v>285</v>
+      </c>
+      <c r="B156" t="s">
+        <v>286</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D156" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" t="s">
+        <v>287</v>
+      </c>
+      <c r="B157" t="s">
+        <v>288</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D157" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" t="s">
+        <v>289</v>
+      </c>
+      <c r="B158" t="s">
+        <v>290</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D158" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" t="s">
+        <v>291</v>
+      </c>
+      <c r="B159" t="s">
+        <v>292</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D159" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" t="s">
+        <v>293</v>
+      </c>
+      <c r="B160" t="s">
+        <v>294</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D160" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" t="s">
+        <v>295</v>
+      </c>
+      <c r="B161" t="s">
+        <v>296</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D161" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" t="s">
+        <v>297</v>
+      </c>
+      <c r="B162" t="s">
+        <v>298</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D162" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" t="s">
+        <v>285</v>
+      </c>
+      <c r="B163" t="s">
+        <v>299</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D163" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" t="s">
+        <v>300</v>
+      </c>
+      <c r="B164" t="s">
+        <v>301</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D164" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" t="s">
+        <v>291</v>
+      </c>
+      <c r="B165" t="s">
+        <v>302</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D165" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" t="s">
+        <v>303</v>
+      </c>
+      <c r="B166" t="s">
+        <v>304</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D166" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" t="s">
+        <v>285</v>
+      </c>
+      <c r="B167" t="s">
+        <v>305</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D167" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" t="s">
+        <v>306</v>
+      </c>
+      <c r="B168" t="s">
+        <v>307</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D168" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" t="s">
+        <v>308</v>
+      </c>
+      <c r="B169" t="s">
+        <v>309</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D169" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" t="s">
+        <v>310</v>
+      </c>
+      <c r="B170" t="s">
+        <v>311</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D170" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" t="s">
+        <v>312</v>
+      </c>
+      <c r="B171" t="s">
+        <v>313</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D171" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" t="s">
+        <v>314</v>
+      </c>
+      <c r="B172" t="s">
+        <v>315</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D172" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" t="s">
+        <v>316</v>
+      </c>
+      <c r="B173" t="s">
+        <v>317</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D173" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" t="s">
+        <v>318</v>
+      </c>
+      <c r="B174" t="s">
+        <v>319</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D174" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" t="s">
+        <v>291</v>
+      </c>
+      <c r="B175" t="s">
+        <v>320</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D175" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" t="s">
+        <v>321</v>
+      </c>
+      <c r="B176" t="s">
+        <v>322</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D176" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" t="s">
+        <v>323</v>
+      </c>
+      <c r="B177" t="s">
+        <v>324</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D177" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" t="s">
+        <v>321</v>
+      </c>
+      <c r="B178" t="s">
+        <v>322</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D178" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" t="s">
+        <v>325</v>
+      </c>
+      <c r="B179" t="s">
+        <v>326</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D179" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" t="s">
+        <v>327</v>
+      </c>
+      <c r="B180" t="s">
+        <v>328</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D180" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" t="s">
+        <v>329</v>
+      </c>
+      <c r="B181" t="s">
+        <v>330</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D181" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" t="s">
+        <v>331</v>
+      </c>
+      <c r="B182" t="s">
+        <v>332</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D182" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" t="s">
+        <v>333</v>
+      </c>
+      <c r="B183" t="s">
+        <v>334</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D183" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" t="s">
+        <v>335</v>
+      </c>
+      <c r="B184" t="s">
+        <v>336</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D184" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" t="s">
+        <v>337</v>
+      </c>
+      <c r="B185" t="s">
+        <v>338</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D185" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" t="s">
+        <v>339</v>
+      </c>
+      <c r="B186" t="s">
+        <v>340</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D186" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" t="s">
+        <v>341</v>
+      </c>
+      <c r="B187" t="s">
+        <v>342</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D187" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" t="s">
+        <v>343</v>
+      </c>
+      <c r="B188" t="s">
+        <v>344</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D188" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" t="s">
+        <v>345</v>
+      </c>
+      <c r="B189" t="s">
+        <v>346</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D189" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" t="s">
+        <v>347</v>
+      </c>
+      <c r="B190" t="s">
+        <v>348</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D190" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" t="s">
+        <v>349</v>
+      </c>
+      <c r="B191" t="s">
+        <v>350</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" t="s">
+        <v>351</v>
+      </c>
+      <c r="B192" t="s">
+        <v>352</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" t="s">
+        <v>353</v>
+      </c>
+      <c r="B193" t="s">
+        <v>354</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" t="s">
+        <v>355</v>
+      </c>
+      <c r="B194" t="s">
+        <v>356</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" t="s">
+        <v>357</v>
+      </c>
+      <c r="B195" t="s">
+        <v>358</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" t="s">
+        <v>359</v>
+      </c>
+      <c r="B196" t="s">
+        <v>360</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D196" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" t="s">
+        <v>361</v>
+      </c>
+      <c r="B197" t="s">
+        <v>362</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D197" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" t="s">
+        <v>363</v>
+      </c>
+      <c r="B198" t="s">
+        <v>364</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D198" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" t="s">
+        <v>365</v>
+      </c>
+      <c r="B199" t="s">
+        <v>366</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" t="s">
+        <v>367</v>
+      </c>
+      <c r="B200" t="s">
+        <v>368</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D200" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" t="s">
+        <v>369</v>
+      </c>
+      <c r="B201" t="s">
+        <v>370</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D201" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" t="s">
+        <v>371</v>
+      </c>
+      <c r="B202" t="s">
+        <v>372</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D202" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" t="s">
+        <v>335</v>
+      </c>
+      <c r="B203" t="s">
+        <v>373</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" t="s">
+        <v>337</v>
+      </c>
+      <c r="B204" t="s">
+        <v>374</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D204" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" t="s">
+        <v>276</v>
+      </c>
+      <c r="B205" t="s">
+        <v>375</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D205" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" t="s">
+        <v>376</v>
+      </c>
+      <c r="B206" t="s">
+        <v>377</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D206" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
+      <c r="A207" t="s">
+        <v>378</v>
+      </c>
+      <c r="B207" t="s">
+        <v>379</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D207" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" t="s">
+        <v>380</v>
+      </c>
+      <c r="B208" t="s">
+        <v>381</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D208" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" t="s">
+        <v>382</v>
+      </c>
+      <c r="B209" t="s">
+        <v>383</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D209" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" t="s">
+        <v>384</v>
+      </c>
+      <c r="B210" t="s">
+        <v>385</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D210" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" t="s">
+        <v>386</v>
+      </c>
+      <c r="B211" t="s">
+        <v>387</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D211" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" t="s">
+        <v>388</v>
+      </c>
+      <c r="B212" t="s">
+        <v>389</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D212" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" t="s">
+        <v>390</v>
+      </c>
+      <c r="B213" t="s">
+        <v>391</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D213" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" t="s">
+        <v>363</v>
+      </c>
+      <c r="B214" t="s">
+        <v>392</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D214" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" t="s">
+        <v>393</v>
+      </c>
+      <c r="B215" t="s">
+        <v>394</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D215" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" t="s">
+        <v>395</v>
+      </c>
+      <c r="B216" t="s">
+        <v>396</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D216" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="A217" t="s">
+        <v>384</v>
+      </c>
+      <c r="B217" t="s">
+        <v>385</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D217" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="A218" t="s">
+        <v>397</v>
+      </c>
+      <c r="B218" t="s">
+        <v>398</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D218" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="A219" t="s">
+        <v>382</v>
+      </c>
+      <c r="B219" t="s">
+        <v>399</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D219" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" t="s">
+        <v>388</v>
+      </c>
+      <c r="B220" t="s">
+        <v>400</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D220" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="A221" t="s">
+        <v>401</v>
+      </c>
+      <c r="B221" t="s">
+        <v>402</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D221" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="A222" t="s">
+        <v>403</v>
+      </c>
+      <c r="B222" t="s">
+        <v>404</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="A223" t="s">
+        <v>405</v>
+      </c>
+      <c r="B223" t="s">
+        <v>406</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D223" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" t="s">
+        <v>384</v>
+      </c>
+      <c r="B224" t="s">
+        <v>407</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D224" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" t="s">
+        <v>408</v>
+      </c>
+      <c r="B225" t="s">
+        <v>409</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D225" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" t="s">
+        <v>410</v>
+      </c>
+      <c r="B226" t="s">
+        <v>411</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D226" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" t="s">
+        <v>388</v>
+      </c>
+      <c r="B227" t="s">
+        <v>412</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D227" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" t="s">
+        <v>413</v>
+      </c>
+      <c r="B228" t="s">
+        <v>414</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D228" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
+        <v>415</v>
+      </c>
+      <c r="B229" t="s">
+        <v>416</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D229" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
+        <v>417</v>
+      </c>
+      <c r="B230" t="s">
+        <v>418</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D230" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
+        <v>419</v>
+      </c>
+      <c r="B231" t="s">
+        <v>420</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D231" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
+        <v>421</v>
+      </c>
+      <c r="B232" t="s">
+        <v>422</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D232" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
+        <v>423</v>
+      </c>
+      <c r="B233" t="s">
+        <v>424</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D233" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
+        <v>425</v>
+      </c>
+      <c r="B234" t="s">
+        <v>426</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D234" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
+        <v>427</v>
+      </c>
+      <c r="B235" t="s">
+        <v>428</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D235" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
+        <v>429</v>
+      </c>
+      <c r="B236" t="s">
+        <v>430</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D236" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
+        <v>431</v>
+      </c>
+      <c r="B237" t="s">
+        <v>432</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D237" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
+        <v>433</v>
+      </c>
+      <c r="B238" t="s">
+        <v>434</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D238" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>435</v>
+      </c>
+      <c r="B239" t="s">
+        <v>436</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D239" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>437</v>
+      </c>
+      <c r="B240" t="s">
+        <v>438</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D240" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>439</v>
+      </c>
+      <c r="B241" t="s">
+        <v>440</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D241" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>441</v>
+      </c>
+      <c r="B242" t="s">
+        <v>442</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D242" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
+        <v>443</v>
+      </c>
+      <c r="B243" t="s">
+        <v>444</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D243" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
+        <v>421</v>
+      </c>
+      <c r="B244" t="s">
+        <v>445</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D244" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
+        <v>446</v>
+      </c>
+      <c r="B245" t="s">
+        <v>447</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D245" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
+        <v>448</v>
+      </c>
+      <c r="B246" t="s">
+        <v>449</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D246" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
+        <v>450</v>
+      </c>
+      <c r="B247" t="s">
+        <v>451</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D247" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" t="s">
+        <v>421</v>
+      </c>
+      <c r="B248" t="s">
+        <v>452</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D248" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" t="s">
+        <v>453</v>
+      </c>
+      <c r="B249" t="s">
+        <v>454</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D249" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" t="s">
+        <v>455</v>
+      </c>
+      <c r="B250" t="s">
+        <v>456</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D250" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" t="s">
+        <v>443</v>
+      </c>
+      <c r="B251" t="s">
+        <v>457</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D251" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" t="s">
+        <v>458</v>
+      </c>
+      <c r="B252" t="s">
+        <v>459</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D252" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" t="s">
+        <v>443</v>
+      </c>
+      <c r="B253" t="s">
+        <v>460</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D253" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" t="s">
+        <v>461</v>
+      </c>
+      <c r="B254" t="s">
+        <v>462</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D254" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" t="s">
+        <v>463</v>
+      </c>
+      <c r="B255" t="s">
+        <v>464</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D255" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" t="s">
+        <v>435</v>
+      </c>
+      <c r="B256" t="s">
+        <v>465</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D256" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
+      <c r="A257" t="s">
+        <v>435</v>
+      </c>
+      <c r="B257" t="s">
+        <v>466</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D257" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
+      <c r="A258" t="s">
+        <v>446</v>
+      </c>
+      <c r="B258" t="s">
+        <v>467</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D258" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
+      <c r="A259" t="s">
+        <v>468</v>
+      </c>
+      <c r="B259" t="s">
+        <v>469</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D259" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
+      <c r="A260" t="s">
+        <v>470</v>
+      </c>
+      <c r="B260" t="s">
+        <v>471</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D260" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
+      <c r="A261" t="s">
+        <v>472</v>
+      </c>
+      <c r="B261" t="s">
+        <v>473</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D261" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
+      <c r="A262" t="s">
+        <v>474</v>
+      </c>
+      <c r="B262" t="s">
+        <v>475</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D262" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
+      <c r="A263" t="s">
+        <v>476</v>
+      </c>
+      <c r="B263" t="s">
+        <v>477</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D263" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
+      <c r="A264" t="s">
+        <v>478</v>
+      </c>
+      <c r="B264" t="s">
+        <v>479</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D264" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
+      <c r="A265" t="s">
+        <v>472</v>
+      </c>
+      <c r="B265" t="s">
+        <v>480</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D265" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" t="s">
+        <v>470</v>
+      </c>
+      <c r="B266" t="s">
+        <v>481</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D266" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" t="s">
+        <v>482</v>
+      </c>
+      <c r="B267" t="s">
+        <v>483</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D267" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
+      <c r="A268" t="s">
+        <v>484</v>
+      </c>
+      <c r="B268" t="s">
+        <v>485</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D268" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
+      <c r="A269" t="s">
+        <v>486</v>
+      </c>
+      <c r="B269" t="s">
+        <v>487</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D269" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" t="s">
+        <v>488</v>
+      </c>
+      <c r="B270" t="s">
+        <v>489</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D270" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" t="s">
+        <v>490</v>
+      </c>
+      <c r="B271" t="s">
+        <v>491</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D271" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
+      <c r="A272" t="s">
+        <v>492</v>
+      </c>
+      <c r="B272" t="s">
+        <v>493</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D272" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" t="s">
+        <v>494</v>
+      </c>
+      <c r="B273" t="s">
+        <v>495</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D273" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" t="s">
+        <v>496</v>
+      </c>
+      <c r="B274" t="s">
+        <v>497</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D274" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" t="s">
+        <v>498</v>
+      </c>
+      <c r="B275" t="s">
+        <v>499</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D275" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" t="s">
+        <v>494</v>
+      </c>
+      <c r="B276" t="s">
+        <v>500</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D276" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" t="s">
+        <v>501</v>
+      </c>
+      <c r="B277" t="s">
+        <v>502</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D277" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" t="s">
+        <v>503</v>
+      </c>
+      <c r="B278" t="s">
+        <v>504</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D278" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" t="s">
+        <v>505</v>
+      </c>
+      <c r="B279" t="s">
+        <v>506</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D279" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" t="s">
+        <v>507</v>
+      </c>
+      <c r="B280" t="s">
+        <v>508</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D280" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" t="s">
+        <v>509</v>
+      </c>
+      <c r="B281" t="s">
+        <v>510</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D281" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" t="s">
+        <v>511</v>
+      </c>
+      <c r="B282" t="s">
+        <v>512</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D282" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" t="s">
+        <v>513</v>
+      </c>
+      <c r="B283" t="s">
+        <v>514</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D283" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" t="s">
+        <v>515</v>
+      </c>
+      <c r="B284" t="s">
+        <v>516</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D284" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" t="s">
+        <v>517</v>
+      </c>
+      <c r="B285" t="s">
+        <v>518</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D285" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" t="s">
+        <v>519</v>
+      </c>
+      <c r="B286" t="s">
+        <v>520</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D286" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" t="s">
+        <v>521</v>
+      </c>
+      <c r="B287" t="s">
+        <v>522</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D287" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" t="s">
+        <v>523</v>
+      </c>
+      <c r="B288" t="s">
+        <v>524</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D288" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" t="s">
+        <v>525</v>
+      </c>
+      <c r="B289" t="s">
+        <v>526</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D289" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" t="s">
+        <v>527</v>
+      </c>
+      <c r="B290" t="s">
+        <v>528</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D290" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" t="s">
+        <v>529</v>
+      </c>
+      <c r="B291" t="s">
+        <v>530</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D291" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" t="s">
+        <v>531</v>
+      </c>
+      <c r="B292" t="s">
+        <v>532</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D292" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" t="s">
+        <v>533</v>
+      </c>
+      <c r="B293" t="s">
+        <v>534</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D293" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" t="s">
+        <v>535</v>
+      </c>
+      <c r="B294" t="s">
+        <v>536</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D294" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" t="s">
+        <v>537</v>
+      </c>
+      <c r="B295" t="s">
+        <v>538</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D295" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" t="s">
+        <v>539</v>
+      </c>
+      <c r="B296" t="s">
+        <v>540</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D296" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" t="s">
+        <v>541</v>
+      </c>
+      <c r="B297" t="s">
+        <v>542</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D297" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" t="s">
+        <v>543</v>
+      </c>
+      <c r="B298" t="s">
+        <v>544</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D298" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" t="s">
+        <v>545</v>
+      </c>
+      <c r="B299" t="s">
+        <v>546</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D299" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" t="s">
+        <v>547</v>
+      </c>
+      <c r="B300" t="s">
+        <v>548</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D300" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" t="s">
+        <v>549</v>
+      </c>
+      <c r="B301" t="s">
+        <v>550</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D301" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" t="s">
+        <v>551</v>
+      </c>
+      <c r="B302" t="s">
+        <v>552</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D302" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" t="s">
+        <v>553</v>
+      </c>
+      <c r="B303" t="s">
+        <v>554</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D303" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" t="s">
+        <v>555</v>
+      </c>
+      <c r="B304" t="s">
+        <v>556</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D304" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
+      <c r="A305" t="s">
+        <v>557</v>
+      </c>
+      <c r="B305" t="s">
+        <v>558</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D305" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
+      <c r="A306" t="s">
+        <v>559</v>
+      </c>
+      <c r="B306" t="s">
+        <v>560</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D306" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
+      <c r="A307" t="s">
+        <v>561</v>
+      </c>
+      <c r="B307" t="s">
+        <v>562</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D307" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
+      <c r="A308" t="s">
+        <v>563</v>
+      </c>
+      <c r="B308" t="s">
+        <v>564</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D308" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" t="s">
+        <v>507</v>
+      </c>
+      <c r="B309" t="s">
+        <v>565</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D309" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" t="s">
+        <v>511</v>
+      </c>
+      <c r="B310" t="s">
+        <v>566</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D310" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" t="s">
+        <v>567</v>
+      </c>
+      <c r="B311" t="s">
+        <v>568</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D311" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
+      <c r="A312" t="s">
+        <v>569</v>
+      </c>
+      <c r="B312" t="s">
+        <v>570</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D312" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
+      <c r="A313" t="s">
+        <v>571</v>
+      </c>
+      <c r="B313" t="s">
+        <v>572</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D313" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
+      <c r="A314" t="s">
+        <v>549</v>
+      </c>
+      <c r="B314" t="s">
+        <v>573</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D314" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
+      <c r="A315" t="s">
+        <v>574</v>
+      </c>
+      <c r="B315" t="s">
+        <v>575</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D315" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
+      <c r="A316" t="s">
+        <v>576</v>
+      </c>
+      <c r="B316" t="s">
+        <v>577</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D316" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
+      <c r="A317" t="s">
+        <v>523</v>
+      </c>
+      <c r="B317" t="s">
+        <v>578</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D317" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
+      <c r="A318" t="s">
+        <v>579</v>
+      </c>
+      <c r="B318" t="s">
+        <v>580</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D318" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
+      <c r="A319" t="s">
+        <v>581</v>
+      </c>
+      <c r="B319" t="s">
+        <v>582</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D319" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
+      <c r="A320" t="s">
+        <v>583</v>
+      </c>
+      <c r="B320" t="s">
+        <v>584</v>
+      </c>
+      <c r="C320" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D320" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
+      <c r="A321" t="s">
+        <v>585</v>
+      </c>
+      <c r="B321" t="s">
+        <v>586</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D321" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
+      <c r="A322" t="s">
+        <v>587</v>
+      </c>
+      <c r="B322" t="s">
+        <v>588</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D322" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
+      <c r="A323" t="s">
+        <v>541</v>
+      </c>
+      <c r="B323" t="s">
+        <v>589</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D323" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
+      <c r="A324" t="s">
+        <v>521</v>
+      </c>
+      <c r="B324" t="s">
+        <v>590</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D324" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
+      <c r="A325" t="s">
+        <v>591</v>
+      </c>
+      <c r="B325" t="s">
+        <v>592</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D325" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
+      <c r="A326" t="s">
+        <v>574</v>
+      </c>
+      <c r="B326" t="s">
+        <v>593</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D326" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
+      <c r="A327" t="s">
+        <v>594</v>
+      </c>
+      <c r="B327" t="s">
+        <v>595</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D327" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
+      <c r="A328" t="s">
+        <v>596</v>
+      </c>
+      <c r="B328" t="s">
+        <v>597</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D328" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
+      <c r="A329" t="s">
+        <v>598</v>
+      </c>
+      <c r="B329" t="s">
+        <v>599</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D329" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
+      <c r="A330" t="s">
+        <v>600</v>
+      </c>
+      <c r="B330" t="s">
+        <v>601</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D330" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
+      <c r="A331" t="s">
+        <v>602</v>
+      </c>
+      <c r="B331" t="s">
+        <v>603</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D331" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
+      <c r="A332" t="s">
+        <v>604</v>
+      </c>
+      <c r="B332" t="s">
+        <v>605</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D332" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
+      <c r="A333" t="s">
+        <v>606</v>
+      </c>
+      <c r="B333" t="s">
+        <v>607</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D333" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
+      <c r="A334" t="s">
+        <v>596</v>
+      </c>
+      <c r="B334" t="s">
+        <v>608</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D334" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
+      <c r="A335" t="s">
+        <v>609</v>
+      </c>
+      <c r="B335" t="s">
+        <v>610</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D335" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
+      <c r="A336" t="s">
+        <v>435</v>
+      </c>
+      <c r="B336" t="s">
+        <v>611</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D336" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
+      <c r="A337" t="s">
+        <v>612</v>
+      </c>
+      <c r="B337" t="s">
+        <v>613</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D337" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
+      <c r="A338" t="s">
+        <v>614</v>
+      </c>
+      <c r="B338" t="s">
+        <v>39</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D338" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
+      <c r="A339" t="s">
+        <v>615</v>
+      </c>
+      <c r="B339" t="s">
+        <v>616</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D339" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
+      <c r="A340" t="s">
+        <v>617</v>
+      </c>
+      <c r="B340" t="s">
+        <v>618</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D340" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
+      <c r="A341" t="s">
+        <v>619</v>
+      </c>
+      <c r="B341" t="s">
+        <v>620</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D341" s="1">
         <v>1</v>
       </c>
     </row>
